--- a/prompts/QTP检查单-全部规则-PDDS.xlsx
+++ b/prompts/QTP检查单-全部规则-PDDS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="30240" windowHeight="13240"/>
   </bookViews>
   <sheets>
     <sheet name="非电磁类" sheetId="1" r:id="rId1"/>
@@ -2339,7 +2339,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2399,6 +2399,17 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2551,16 +2562,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2588,6 +2599,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2630,12 +2647,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3024,137 +3035,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="14">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="14">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="14">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="16">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3308,6 +3319,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3316,6 +3330,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3653,27 +3682,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F269"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="45.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="56.8981481481481" customWidth="1"/>
-    <col min="5" max="5" width="30.8425925925926" customWidth="1"/>
-    <col min="6" max="6" width="42.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="11.8846153846154" customWidth="1"/>
+    <col min="2" max="2" width="18.6634615384615" customWidth="1"/>
+    <col min="3" max="3" width="45.5576923076923" customWidth="1"/>
+    <col min="4" max="4" width="56.8942307692308" customWidth="1"/>
+    <col min="5" max="5" width="30.8461538461538" customWidth="1"/>
+    <col min="6" max="6" width="42.3365384615385" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="50" customFormat="1" spans="1:6">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="53"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
+    </row>
+    <row r="2" ht="17" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3693,7 +3722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="17" spans="1:6">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -3709,7 +3738,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" ht="17" spans="1:6">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -3725,7 +3754,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" ht="28.8" spans="1:6">
+    <row r="5" ht="34" spans="1:6">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -3741,7 +3770,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" ht="28.8" spans="1:6">
+    <row r="6" ht="34" spans="1:6">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -3757,7 +3786,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" ht="28.8" spans="1:6">
+    <row r="7" ht="34" spans="1:6">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -3774,16 +3803,16 @@
       <c r="F7" s="5"/>
     </row>
     <row r="8" s="50" customFormat="1" spans="1:6">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="53"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="54"/>
+    </row>
+    <row r="9" ht="17" spans="1:6">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -3795,7 +3824,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" ht="17" spans="1:6">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -3807,7 +3836,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" ht="17" spans="1:6">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -3825,7 +3854,7 @@
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" ht="17" spans="1:6">
       <c r="A12" s="5">
         <v>4</v>
       </c>
@@ -3837,7 +3866,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" ht="17" spans="1:6">
       <c r="A13" s="5">
         <v>5</v>
       </c>
@@ -3853,7 +3882,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="10"/>
     </row>
-    <row r="14" ht="28.8" spans="1:6">
+    <row r="14" ht="34" spans="1:6">
       <c r="A14" s="5">
         <v>6</v>
       </c>
@@ -3869,7 +3898,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" ht="17" spans="1:6">
       <c r="A15" s="5">
         <v>7</v>
       </c>
@@ -3885,7 +3914,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" ht="17" spans="1:6">
       <c r="A16" s="5">
         <v>8</v>
       </c>
@@ -3901,7 +3930,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" ht="17" spans="1:6">
       <c r="A17" s="5">
         <v>9</v>
       </c>
@@ -3927,7 +3956,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" ht="17" spans="1:6">
       <c r="A19" s="5">
         <v>1</v>
       </c>
@@ -3943,7 +3972,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" ht="34" spans="1:6">
       <c r="A20" s="5">
         <v>2</v>
       </c>
@@ -3959,7 +3988,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" ht="17" spans="1:6">
       <c r="A21" s="5">
         <v>3</v>
       </c>
@@ -3975,7 +4004,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" ht="17" spans="1:6">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -3991,7 +4020,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
     </row>
-    <row r="23" ht="43.2" spans="1:6">
+    <row r="23" ht="51" spans="1:6">
       <c r="A23" s="5">
         <v>5</v>
       </c>
@@ -4010,34 +4039,34 @@
       <c r="F23" s="10"/>
     </row>
     <row r="24" s="50" customFormat="1" spans="1:6">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53"/>
-    </row>
-    <row r="25" ht="28.8" spans="1:6">
-      <c r="A25" s="5">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="54"/>
+    </row>
+    <row r="25" s="51" customFormat="1" ht="34" spans="1:6">
+      <c r="A25" s="55">
         <v>1</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="D25" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" ht="72" spans="1:6">
+      <c r="F25" s="59"/>
+    </row>
+    <row r="26" ht="78" spans="1:6">
       <c r="A26" s="5">
         <v>2</v>
       </c>
@@ -4055,53 +4084,53 @@
       </c>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5">
+    <row r="27" s="51" customFormat="1" ht="34" spans="1:6">
+      <c r="A27" s="55">
         <v>3</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5">
+      <c r="D27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59"/>
+    </row>
+    <row r="28" s="51" customFormat="1" ht="17" spans="1:6">
+      <c r="A28" s="55">
         <v>4</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
+      <c r="D28" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59"/>
     </row>
     <row r="29" s="50" customFormat="1" spans="1:6">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
     </row>
     <row r="30" ht="54" customHeight="1" spans="1:6">
       <c r="A30" s="5">
         <v>1</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="60" t="s">
         <v>58</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -4113,7 +4142,7 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" ht="28.8" spans="1:6">
+    <row r="31" ht="34" spans="1:6">
       <c r="A31" s="5">
         <v>2</v>
       </c>
@@ -4139,7 +4168,7 @@
       <c r="E32" s="17"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" ht="17" spans="1:6">
       <c r="A33" s="4" t="s">
         <v>1</v>
       </c>
@@ -4159,7 +4188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" ht="28.8" spans="1:6">
+    <row r="34" ht="34" spans="1:6">
       <c r="A34" s="5">
         <v>1</v>
       </c>
@@ -4175,7 +4204,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" ht="17" spans="1:6">
       <c r="A35" s="19"/>
       <c r="B35" s="20" t="s">
         <v>66</v>
@@ -4221,7 +4250,7 @@
       <c r="E37" s="11"/>
       <c r="F37" s="23"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" ht="17" spans="1:6">
       <c r="A38" s="29"/>
       <c r="B38" s="30"/>
       <c r="C38" s="11" t="s">
@@ -4257,7 +4286,7 @@
       <c r="E40" s="11"/>
       <c r="F40" s="23"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" ht="17" spans="1:6">
       <c r="A41" s="29"/>
       <c r="B41" s="30"/>
       <c r="C41" s="26" t="s">
@@ -4299,7 +4328,7 @@
       <c r="E43" s="11"/>
       <c r="F43" s="23"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" ht="17" spans="1:6">
       <c r="A44" s="29"/>
       <c r="B44" s="30"/>
       <c r="C44" s="11" t="s">
@@ -4335,7 +4364,7 @@
       <c r="E46" s="11"/>
       <c r="F46" s="23"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" ht="17" spans="1:6">
       <c r="A47" s="29"/>
       <c r="B47" s="44"/>
       <c r="C47" s="26" t="s">
@@ -4377,7 +4406,7 @@
       <c r="E49" s="11"/>
       <c r="F49" s="23"/>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" ht="17" spans="1:6">
       <c r="A50" s="29"/>
       <c r="B50" s="30"/>
       <c r="C50" s="11" t="s">
@@ -4413,7 +4442,7 @@
       <c r="E52" s="11"/>
       <c r="F52" s="23"/>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" ht="17" spans="1:6">
       <c r="A53" s="29"/>
       <c r="B53" s="30"/>
       <c r="C53" s="26" t="s">
@@ -4455,7 +4484,7 @@
       <c r="E55" s="11"/>
       <c r="F55" s="23"/>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" ht="17" spans="1:6">
       <c r="A56" s="29"/>
       <c r="B56" s="30"/>
       <c r="C56" s="11" t="s">
@@ -4491,7 +4520,7 @@
       <c r="E58" s="11"/>
       <c r="F58" s="23"/>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" ht="17" spans="1:6">
       <c r="A59" s="29"/>
       <c r="B59" s="30"/>
       <c r="C59" s="26" t="s">
@@ -4533,7 +4562,7 @@
       <c r="E61" s="11"/>
       <c r="F61" s="23"/>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" ht="17" spans="1:6">
       <c r="A62" s="29"/>
       <c r="B62" s="30"/>
       <c r="C62" s="11" t="s">
@@ -4569,7 +4598,7 @@
       <c r="E64" s="11"/>
       <c r="F64" s="23"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" ht="17" spans="1:6">
       <c r="A65" s="29"/>
       <c r="B65" s="30"/>
       <c r="C65" s="26" t="s">
@@ -4611,7 +4640,7 @@
       <c r="E67" s="11"/>
       <c r="F67" s="32"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" ht="17" spans="1:6">
       <c r="A68" s="29"/>
       <c r="B68" s="30"/>
       <c r="C68" s="11" t="s">
@@ -4647,7 +4676,7 @@
       <c r="E70" s="11"/>
       <c r="F70" s="32"/>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" ht="17" spans="1:6">
       <c r="A71" s="29"/>
       <c r="B71" s="30"/>
       <c r="C71" s="26" t="s">
@@ -4661,11 +4690,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" ht="17" spans="1:6">
       <c r="A72" s="29">
         <v>7</v>
       </c>
-      <c r="B72" s="55" t="s">
+      <c r="B72" s="61" t="s">
         <v>86</v>
       </c>
       <c r="C72" s="26" t="s">
@@ -4677,9 +4706,9 @@
       <c r="E72" s="11"/>
       <c r="F72" s="32"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" ht="34" spans="1:6">
       <c r="A73" s="29"/>
-      <c r="B73" s="55"/>
+      <c r="B73" s="61"/>
       <c r="C73" s="26" t="s">
         <v>88</v>
       </c>
@@ -4691,7 +4720,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="29"/>
-      <c r="B74" s="55"/>
+      <c r="B74" s="61"/>
       <c r="C74" s="11" t="s">
         <v>89</v>
       </c>
@@ -4703,7 +4732,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="29"/>
-      <c r="B75" s="55"/>
+      <c r="B75" s="61"/>
       <c r="C75" s="11" t="s">
         <v>90</v>
       </c>
@@ -4713,9 +4742,9 @@
       <c r="E75" s="11"/>
       <c r="F75" s="32"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" ht="17" spans="1:6">
       <c r="A76" s="29"/>
-      <c r="B76" s="55"/>
+      <c r="B76" s="61"/>
       <c r="C76" s="11" t="s">
         <v>91</v>
       </c>
@@ -4727,7 +4756,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="29"/>
-      <c r="B77" s="55"/>
+      <c r="B77" s="61"/>
       <c r="C77" s="11" t="s">
         <v>93</v>
       </c>
@@ -4739,7 +4768,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="29"/>
-      <c r="B78" s="55"/>
+      <c r="B78" s="61"/>
       <c r="C78" s="11" t="s">
         <v>94</v>
       </c>
@@ -4749,9 +4778,9 @@
       <c r="E78" s="11"/>
       <c r="F78" s="32"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" ht="17" spans="1:6">
       <c r="A79" s="29"/>
-      <c r="B79" s="55"/>
+      <c r="B79" s="61"/>
       <c r="C79" s="26" t="s">
         <v>95</v>
       </c>
@@ -4767,7 +4796,7 @@
       <c r="A80" s="29">
         <v>8</v>
       </c>
-      <c r="B80" s="55" t="s">
+      <c r="B80" s="61" t="s">
         <v>96</v>
       </c>
       <c r="C80" s="11" t="s">
@@ -4781,7 +4810,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="29"/>
-      <c r="B81" s="55"/>
+      <c r="B81" s="61"/>
       <c r="C81" s="11" t="s">
         <v>71</v>
       </c>
@@ -4791,9 +4820,9 @@
       <c r="E81" s="11"/>
       <c r="F81" s="32"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" ht="17" spans="1:6">
       <c r="A82" s="29"/>
-      <c r="B82" s="55"/>
+      <c r="B82" s="61"/>
       <c r="C82" s="11" t="s">
         <v>97</v>
       </c>
@@ -4805,7 +4834,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="29"/>
-      <c r="B83" s="55"/>
+      <c r="B83" s="61"/>
       <c r="C83" s="11" t="s">
         <v>74</v>
       </c>
@@ -4817,7 +4846,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="29"/>
-      <c r="B84" s="55"/>
+      <c r="B84" s="61"/>
       <c r="C84" s="11" t="s">
         <v>75</v>
       </c>
@@ -4827,9 +4856,9 @@
       <c r="E84" s="11"/>
       <c r="F84" s="32"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" ht="17" spans="1:6">
       <c r="A85" s="29"/>
-      <c r="B85" s="55"/>
+      <c r="B85" s="61"/>
       <c r="C85" s="26" t="s">
         <v>77</v>
       </c>
@@ -4845,7 +4874,7 @@
       <c r="A86" s="29">
         <v>9</v>
       </c>
-      <c r="B86" s="55" t="s">
+      <c r="B86" s="61" t="s">
         <v>99</v>
       </c>
       <c r="C86" s="11" t="s">
@@ -4859,7 +4888,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="29"/>
-      <c r="B87" s="55"/>
+      <c r="B87" s="61"/>
       <c r="C87" s="11" t="s">
         <v>71</v>
       </c>
@@ -4871,7 +4900,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="29"/>
-      <c r="B88" s="55"/>
+      <c r="B88" s="61"/>
       <c r="C88" s="11" t="s">
         <v>100</v>
       </c>
@@ -4881,9 +4910,9 @@
       <c r="E88" s="11"/>
       <c r="F88" s="32"/>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" ht="17" spans="1:6">
       <c r="A89" s="29"/>
-      <c r="B89" s="55"/>
+      <c r="B89" s="61"/>
       <c r="C89" s="11" t="s">
         <v>101</v>
       </c>
@@ -4895,7 +4924,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="29"/>
-      <c r="B90" s="55"/>
+      <c r="B90" s="61"/>
       <c r="C90" s="11" t="s">
         <v>103</v>
       </c>
@@ -4907,7 +4936,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="29"/>
-      <c r="B91" s="55"/>
+      <c r="B91" s="61"/>
       <c r="C91" s="11" t="s">
         <v>104</v>
       </c>
@@ -4917,9 +4946,9 @@
       <c r="E91" s="11"/>
       <c r="F91" s="32"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" ht="17" spans="1:6">
       <c r="A92" s="29"/>
-      <c r="B92" s="55"/>
+      <c r="B92" s="61"/>
       <c r="C92" s="26" t="s">
         <v>105</v>
       </c>
@@ -4935,7 +4964,7 @@
       <c r="A93" s="29">
         <v>10</v>
       </c>
-      <c r="B93" s="55" t="s">
+      <c r="B93" s="61" t="s">
         <v>106</v>
       </c>
       <c r="C93" s="11" t="s">
@@ -4949,7 +4978,7 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="29"/>
-      <c r="B94" s="55"/>
+      <c r="B94" s="61"/>
       <c r="C94" s="11" t="s">
         <v>71</v>
       </c>
@@ -4959,9 +4988,9 @@
       <c r="E94" s="11"/>
       <c r="F94" s="32"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" ht="17" spans="1:6">
       <c r="A95" s="29"/>
-      <c r="B95" s="55"/>
+      <c r="B95" s="61"/>
       <c r="C95" s="11" t="s">
         <v>107</v>
       </c>
@@ -4973,7 +5002,7 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="29"/>
-      <c r="B96" s="55"/>
+      <c r="B96" s="61"/>
       <c r="C96" s="11" t="s">
         <v>74</v>
       </c>
@@ -4985,7 +5014,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="29"/>
-      <c r="B97" s="55"/>
+      <c r="B97" s="61"/>
       <c r="C97" s="11" t="s">
         <v>75</v>
       </c>
@@ -4995,9 +5024,9 @@
       <c r="E97" s="11"/>
       <c r="F97" s="32"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" ht="17" spans="1:6">
       <c r="A98" s="29"/>
-      <c r="B98" s="55"/>
+      <c r="B98" s="61"/>
       <c r="C98" s="26" t="s">
         <v>105</v>
       </c>
@@ -5019,7 +5048,7 @@
       <c r="E99" s="17"/>
       <c r="F99" s="18"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" ht="17" spans="1:6">
       <c r="A100" s="4" t="s">
         <v>1</v>
       </c>
@@ -5039,7 +5068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" ht="28.8" spans="1:6">
+    <row r="101" ht="34" spans="1:6">
       <c r="A101" s="5">
         <v>1</v>
       </c>
@@ -5055,7 +5084,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" ht="17" spans="1:6">
       <c r="A102" s="19"/>
       <c r="B102" s="20" t="s">
         <v>66</v>
@@ -5101,7 +5130,7 @@
       <c r="E104" s="11"/>
       <c r="F104" s="23"/>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" ht="17" spans="1:6">
       <c r="A105" s="29"/>
       <c r="B105" s="30"/>
       <c r="C105" s="11" t="s">
@@ -5125,7 +5154,7 @@
       <c r="E106" s="11"/>
       <c r="F106" s="23"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" ht="17" spans="1:6">
       <c r="A107" s="29"/>
       <c r="B107" s="30"/>
       <c r="C107" s="26" t="s">
@@ -5149,7 +5178,7 @@
       <c r="E108" s="17"/>
       <c r="F108" s="18"/>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" ht="17" spans="1:6">
       <c r="A109" s="4" t="s">
         <v>1</v>
       </c>
@@ -5169,7 +5198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" ht="28.8" spans="1:6">
+    <row r="110" ht="34" spans="1:6">
       <c r="A110" s="5">
         <v>1</v>
       </c>
@@ -5185,7 +5214,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" ht="17" spans="1:6">
       <c r="A111" s="19"/>
       <c r="B111" s="20" t="s">
         <v>66</v>
@@ -5255,7 +5284,7 @@
       <c r="E115" s="11"/>
       <c r="F115" s="32"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" ht="17" spans="1:6">
       <c r="A116" s="29"/>
       <c r="B116" s="30"/>
       <c r="C116" s="26" t="s">
@@ -5279,7 +5308,7 @@
       <c r="E117" s="17"/>
       <c r="F117" s="18"/>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" ht="17" spans="1:6">
       <c r="A118" s="4" t="s">
         <v>1</v>
       </c>
@@ -5299,7 +5328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" ht="28.8" spans="1:6">
+    <row r="119" ht="34" spans="1:6">
       <c r="A119" s="5">
         <v>1</v>
       </c>
@@ -5315,7 +5344,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" ht="17" spans="1:6">
       <c r="A120" s="19"/>
       <c r="B120" s="20" t="s">
         <v>66</v>
@@ -5333,7 +5362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" ht="43.2" spans="1:6">
+    <row r="121" ht="51" spans="1:6">
       <c r="A121" s="47">
         <v>1</v>
       </c>
@@ -5351,7 +5380,7 @@
       </c>
       <c r="F121" s="48"/>
     </row>
-    <row r="122" ht="28.8" spans="1:6">
+    <row r="122" ht="34" spans="1:6">
       <c r="A122" s="47"/>
       <c r="B122" s="47"/>
       <c r="C122" s="26" t="s">
@@ -5363,7 +5392,7 @@
       <c r="E122" s="11"/>
       <c r="F122" s="48"/>
     </row>
-    <row r="123" ht="28.8" spans="1:6">
+    <row r="123" ht="36" spans="1:6">
       <c r="A123" s="47"/>
       <c r="B123" s="47"/>
       <c r="C123" s="35" t="s">
@@ -5377,7 +5406,7 @@
       </c>
       <c r="F123" s="48"/>
     </row>
-    <row r="124" ht="46.8" spans="1:6">
+    <row r="124" ht="53" spans="1:6">
       <c r="A124" s="47"/>
       <c r="B124" s="47"/>
       <c r="C124" s="35" t="s">
@@ -5389,7 +5418,7 @@
       <c r="E124" s="39"/>
       <c r="F124" s="48"/>
     </row>
-    <row r="125" ht="31.2" spans="1:6">
+    <row r="125" ht="36" spans="1:6">
       <c r="A125" s="47">
         <v>2</v>
       </c>
@@ -5419,7 +5448,7 @@
       <c r="E126" s="45"/>
       <c r="F126" s="48"/>
     </row>
-    <row r="127" ht="31.2" spans="1:6">
+    <row r="127" ht="36" spans="1:6">
       <c r="A127" s="47"/>
       <c r="B127" s="47"/>
       <c r="C127" s="35" t="s">
@@ -5431,7 +5460,7 @@
       <c r="E127" s="45"/>
       <c r="F127" s="48"/>
     </row>
-    <row r="128" ht="31.2" spans="1:6">
+    <row r="128" ht="36" spans="1:6">
       <c r="A128" s="47"/>
       <c r="B128" s="47" t="s">
         <v>133</v>
@@ -5457,7 +5486,7 @@
       <c r="E129" s="45"/>
       <c r="F129" s="48"/>
     </row>
-    <row r="130" ht="31.2" spans="1:6">
+    <row r="130" ht="36" spans="1:6">
       <c r="A130" s="47"/>
       <c r="B130" s="47" t="s">
         <v>136</v>
@@ -5483,7 +5512,7 @@
       <c r="E131" s="45"/>
       <c r="F131" s="48"/>
     </row>
-    <row r="132" ht="31.2" spans="1:6">
+    <row r="132" ht="36" spans="1:6">
       <c r="A132" s="47"/>
       <c r="B132" s="47" t="s">
         <v>139</v>
@@ -5521,7 +5550,7 @@
       <c r="E134" s="45"/>
       <c r="F134" s="48"/>
     </row>
-    <row r="135" ht="31.2" spans="1:6">
+    <row r="135" ht="36" spans="1:6">
       <c r="A135" s="47">
         <v>3</v>
       </c>
@@ -5539,7 +5568,7 @@
       </c>
       <c r="F135" s="48"/>
     </row>
-    <row r="136" ht="31.2" spans="1:6">
+    <row r="136" ht="36" spans="1:6">
       <c r="A136" s="47"/>
       <c r="B136" s="47"/>
       <c r="C136" s="35" t="s">
@@ -5573,7 +5602,7 @@
       <c r="E138" s="17"/>
       <c r="F138" s="18"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" ht="17" spans="1:6">
       <c r="A139" s="4" t="s">
         <v>1</v>
       </c>
@@ -5593,7 +5622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" ht="28.8" spans="1:6">
+    <row r="140" ht="34" spans="1:6">
       <c r="A140" s="5">
         <v>1</v>
       </c>
@@ -5609,7 +5638,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" ht="17" spans="1:6">
       <c r="A141" s="19"/>
       <c r="B141" s="20" t="s">
         <v>66</v>
@@ -5627,7 +5656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" ht="43.2" spans="1:6">
+    <row r="142" ht="51" spans="1:6">
       <c r="A142" s="47">
         <v>1</v>
       </c>
@@ -5645,7 +5674,7 @@
       </c>
       <c r="F142" s="36"/>
     </row>
-    <row r="143" ht="31.2" spans="1:6">
+    <row r="143" ht="36" spans="1:6">
       <c r="A143" s="47"/>
       <c r="B143" s="47"/>
       <c r="C143" s="35" t="s">
@@ -5657,7 +5686,7 @@
       <c r="E143" s="11"/>
       <c r="F143" s="36"/>
     </row>
-    <row r="144" ht="28.8" spans="1:6">
+    <row r="144" ht="36" spans="1:6">
       <c r="A144" s="47"/>
       <c r="B144" s="47"/>
       <c r="C144" s="35" t="s">
@@ -5683,7 +5712,7 @@
       <c r="E145" s="38"/>
       <c r="F145" s="36"/>
     </row>
-    <row r="146" ht="31.2" spans="1:6">
+    <row r="146" ht="36" spans="1:6">
       <c r="A146" s="47"/>
       <c r="B146" s="47"/>
       <c r="C146" s="39" t="s">
@@ -5695,7 +5724,7 @@
       <c r="E146" s="39"/>
       <c r="F146" s="36"/>
     </row>
-    <row r="147" ht="46.8" spans="1:6">
+    <row r="147" ht="53" spans="1:6">
       <c r="A147" s="47">
         <v>2</v>
       </c>
@@ -5711,7 +5740,7 @@
       <c r="E147" s="40"/>
       <c r="F147" s="36"/>
     </row>
-    <row r="148" ht="15.6" spans="1:6">
+    <row r="148" ht="18" spans="1:6">
       <c r="A148" s="47"/>
       <c r="B148" s="47"/>
       <c r="C148" s="35" t="s">
@@ -5723,7 +5752,7 @@
       <c r="E148" s="40"/>
       <c r="F148" s="36"/>
     </row>
-    <row r="149" ht="31.2" spans="1:6">
+    <row r="149" ht="36" spans="1:6">
       <c r="A149" s="47"/>
       <c r="B149" s="47"/>
       <c r="C149" s="35" t="s">
@@ -5735,7 +5764,7 @@
       <c r="E149" s="40"/>
       <c r="F149" s="36"/>
     </row>
-    <row r="150" ht="46.8" spans="1:6">
+    <row r="150" ht="53" spans="1:6">
       <c r="A150" s="47"/>
       <c r="B150" s="47" t="s">
         <v>155</v>
@@ -5749,7 +5778,7 @@
       <c r="E150" s="40"/>
       <c r="F150" s="36"/>
     </row>
-    <row r="151" ht="15.6" spans="1:6">
+    <row r="151" ht="18" spans="1:6">
       <c r="A151" s="47"/>
       <c r="B151" s="47"/>
       <c r="C151" s="35" t="s">
@@ -5761,10 +5790,10 @@
       <c r="E151" s="40"/>
       <c r="F151" s="36"/>
     </row>
-    <row r="152" ht="15.6" spans="1:6">
+    <row r="152" ht="17.6" spans="1:6">
       <c r="A152" s="47"/>
       <c r="B152" s="47"/>
-      <c r="C152" s="56" t="s">
+      <c r="C152" s="62" t="s">
         <v>157</v>
       </c>
       <c r="D152" s="11" t="s">
@@ -5773,7 +5802,7 @@
       <c r="E152" s="40"/>
       <c r="F152" s="36"/>
     </row>
-    <row r="153" ht="46.8" spans="1:6">
+    <row r="153" ht="53" spans="1:6">
       <c r="A153" s="47"/>
       <c r="B153" s="47" t="s">
         <v>158</v>
@@ -5787,7 +5816,7 @@
       <c r="E153" s="40"/>
       <c r="F153" s="36"/>
     </row>
-    <row r="154" ht="15.6" spans="1:6">
+    <row r="154" ht="18" spans="1:6">
       <c r="A154" s="47"/>
       <c r="B154" s="47"/>
       <c r="C154" s="35" t="s">
@@ -5799,7 +5828,7 @@
       <c r="E154" s="40"/>
       <c r="F154" s="36"/>
     </row>
-    <row r="155" ht="31.2" spans="1:6">
+    <row r="155" ht="36" spans="1:6">
       <c r="A155" s="47">
         <v>3</v>
       </c>
@@ -5817,7 +5846,7 @@
       </c>
       <c r="F155" s="36"/>
     </row>
-    <row r="156" ht="31.2" spans="1:6">
+    <row r="156" ht="36" spans="1:6">
       <c r="A156" s="47"/>
       <c r="B156" s="47"/>
       <c r="C156" s="35" t="s">
@@ -5829,7 +5858,7 @@
       <c r="E156" s="47"/>
       <c r="F156" s="36"/>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" ht="17" spans="1:6">
       <c r="A157" s="47"/>
       <c r="B157" s="47"/>
       <c r="C157" s="26" t="s">
@@ -5851,7 +5880,7 @@
       <c r="E158" s="17"/>
       <c r="F158" s="18"/>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" ht="17" spans="1:6">
       <c r="A159" s="4" t="s">
         <v>1</v>
       </c>
@@ -5871,7 +5900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" ht="28.8" spans="1:6">
+    <row r="160" ht="34" spans="1:6">
       <c r="A160" s="5">
         <v>1</v>
       </c>
@@ -5887,7 +5916,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" ht="17" spans="1:6">
       <c r="A161" s="19"/>
       <c r="B161" s="20" t="s">
         <v>66</v>
@@ -5905,7 +5934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" ht="15.6" spans="1:6">
+    <row r="162" ht="18" spans="1:6">
       <c r="A162" s="47">
         <v>1</v>
       </c>
@@ -5921,7 +5950,7 @@
       <c r="E162" s="40"/>
       <c r="F162" s="36"/>
     </row>
-    <row r="163" ht="31.2" spans="1:6">
+    <row r="163" ht="36" spans="1:6">
       <c r="A163" s="47"/>
       <c r="B163" s="47"/>
       <c r="C163" s="35" t="s">
@@ -5933,7 +5962,7 @@
       <c r="E163" s="40"/>
       <c r="F163" s="36"/>
     </row>
-    <row r="164" ht="31.2" spans="1:6">
+    <row r="164" ht="36" spans="1:6">
       <c r="A164" s="47"/>
       <c r="B164" s="47"/>
       <c r="C164" s="35" t="s">
@@ -5945,7 +5974,7 @@
       <c r="E164" s="40"/>
       <c r="F164" s="36"/>
     </row>
-    <row r="165" ht="124.8" spans="1:6">
+    <row r="165" ht="141" spans="1:6">
       <c r="A165" s="47"/>
       <c r="B165" s="47"/>
       <c r="C165" s="26" t="s">
@@ -5969,7 +5998,7 @@
       <c r="E166" s="17"/>
       <c r="F166" s="18"/>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" ht="17" spans="1:6">
       <c r="A167" s="4" t="s">
         <v>1</v>
       </c>
@@ -5989,7 +6018,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" ht="129.6" spans="1:6">
+    <row r="168" ht="152" spans="1:6">
       <c r="A168" s="5">
         <v>1</v>
       </c>
@@ -6005,7 +6034,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" ht="17" spans="1:6">
       <c r="A169" s="19"/>
       <c r="B169" s="20" t="s">
         <v>66</v>
@@ -6023,7 +6052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" ht="31.2" spans="1:6">
+    <row r="170" ht="36" spans="1:6">
       <c r="A170" s="47">
         <v>1</v>
       </c>
@@ -6041,7 +6070,7 @@
       </c>
       <c r="F170" s="43"/>
     </row>
-    <row r="171" ht="93.6" spans="1:6">
+    <row r="171" ht="106" spans="1:6">
       <c r="A171" s="47"/>
       <c r="B171" s="47"/>
       <c r="C171" s="35" t="s">
@@ -6053,7 +6082,7 @@
       <c r="E171" s="45"/>
       <c r="F171" s="43"/>
     </row>
-    <row r="172" ht="31.2" spans="1:6">
+    <row r="172" ht="36" spans="1:6">
       <c r="A172" s="47"/>
       <c r="B172" s="47" t="s">
         <v>175</v>
@@ -6069,7 +6098,7 @@
       </c>
       <c r="F172" s="43"/>
     </row>
-    <row r="173" ht="72" spans="1:6">
+    <row r="173" ht="84" spans="1:6">
       <c r="A173" s="47"/>
       <c r="B173" s="47"/>
       <c r="C173" s="44" t="s">
@@ -6081,7 +6110,7 @@
       <c r="E173" s="45"/>
       <c r="F173" s="43"/>
     </row>
-    <row r="174" ht="28.8" spans="1:6">
+    <row r="174" ht="34" spans="1:6">
       <c r="A174" s="47"/>
       <c r="B174" s="47" t="s">
         <v>179</v>
@@ -6097,7 +6126,7 @@
       </c>
       <c r="F174" s="43"/>
     </row>
-    <row r="175" ht="86.4" spans="1:6">
+    <row r="175" ht="101" spans="1:6">
       <c r="A175" s="47"/>
       <c r="B175" s="47"/>
       <c r="C175" s="44" t="s">
@@ -6109,7 +6138,7 @@
       <c r="E175" s="45"/>
       <c r="F175" s="43"/>
     </row>
-    <row r="176" ht="28.8" spans="1:6">
+    <row r="176" ht="34" spans="1:6">
       <c r="A176" s="47"/>
       <c r="B176" s="47" t="s">
         <v>183</v>
@@ -6125,7 +6154,7 @@
       </c>
       <c r="F176" s="43"/>
     </row>
-    <row r="177" ht="72" spans="1:6">
+    <row r="177" ht="84" spans="1:6">
       <c r="A177" s="47"/>
       <c r="B177" s="47"/>
       <c r="C177" s="44" t="s">
@@ -6137,14 +6166,14 @@
       <c r="E177" s="45"/>
       <c r="F177" s="43"/>
     </row>
-    <row r="178" ht="28.8" spans="1:6">
+    <row r="178" ht="34" spans="1:6">
       <c r="A178" s="43">
         <v>2</v>
       </c>
       <c r="B178" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C178" s="57" t="s">
+      <c r="C178" s="63" t="s">
         <v>187</v>
       </c>
       <c r="D178" s="44" t="s">
@@ -6165,7 +6194,7 @@
       <c r="E179" s="17"/>
       <c r="F179" s="18"/>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" ht="17" spans="1:6">
       <c r="A180" s="4" t="s">
         <v>1</v>
       </c>
@@ -6185,7 +6214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" ht="201.6" spans="1:6">
+    <row r="181" ht="236" spans="1:6">
       <c r="A181" s="5">
         <v>1</v>
       </c>
@@ -6201,7 +6230,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" ht="17" spans="1:6">
       <c r="A182" s="19"/>
       <c r="B182" s="20" t="s">
         <v>66</v>
@@ -6219,7 +6248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" ht="31.2" spans="1:6">
+    <row r="183" ht="36" spans="1:6">
       <c r="A183" s="47">
         <v>1</v>
       </c>
@@ -6237,7 +6266,7 @@
       </c>
       <c r="F183" s="43"/>
     </row>
-    <row r="184" ht="124.8" spans="1:6">
+    <row r="184" ht="141" spans="1:6">
       <c r="A184" s="47"/>
       <c r="B184" s="47"/>
       <c r="C184" s="35" t="s">
@@ -6249,7 +6278,7 @@
       <c r="E184" s="45"/>
       <c r="F184" s="43"/>
     </row>
-    <row r="185" ht="31.2" spans="1:6">
+    <row r="185" ht="36" spans="1:6">
       <c r="A185" s="47"/>
       <c r="B185" s="47" t="s">
         <v>195</v>
@@ -6265,7 +6294,7 @@
       </c>
       <c r="F185" s="43"/>
     </row>
-    <row r="186" ht="115.2" spans="1:6">
+    <row r="186" ht="152" spans="1:6">
       <c r="A186" s="47"/>
       <c r="B186" s="47"/>
       <c r="C186" s="44" t="s">
@@ -6277,14 +6306,14 @@
       <c r="E186" s="45"/>
       <c r="F186" s="43"/>
     </row>
-    <row r="187" ht="28.8" spans="1:6">
+    <row r="187" ht="34" spans="1:6">
       <c r="A187" s="43">
         <v>2</v>
       </c>
       <c r="B187" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C187" s="57" t="s">
+      <c r="C187" s="63" t="s">
         <v>187</v>
       </c>
       <c r="D187" s="44" t="s">
@@ -6305,7 +6334,7 @@
       <c r="E188" s="17"/>
       <c r="F188" s="18"/>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" ht="17" spans="1:6">
       <c r="A189" s="4" t="s">
         <v>1</v>
       </c>
@@ -6325,7 +6354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" ht="28.8" spans="1:6">
+    <row r="190" ht="34" spans="1:6">
       <c r="A190" s="5">
         <v>1</v>
       </c>
@@ -6341,7 +6370,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" ht="17" spans="1:6">
       <c r="A191" s="19"/>
       <c r="B191" s="20" t="s">
         <v>66</v>
@@ -6359,7 +6388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" ht="31.2" spans="1:6">
+    <row r="192" ht="36" spans="1:6">
       <c r="A192" s="47">
         <v>1</v>
       </c>
@@ -6375,7 +6404,7 @@
       <c r="E192" s="40"/>
       <c r="F192" s="43"/>
     </row>
-    <row r="193" ht="15.6" spans="1:6">
+    <row r="193" ht="18" spans="1:6">
       <c r="A193" s="47"/>
       <c r="B193" s="47"/>
       <c r="C193" s="35" t="s">
@@ -6387,7 +6416,7 @@
       <c r="E193" s="40"/>
       <c r="F193" s="43"/>
     </row>
-    <row r="194" ht="31.2" spans="1:6">
+    <row r="194" ht="36" spans="1:6">
       <c r="A194" s="47"/>
       <c r="B194" s="47"/>
       <c r="C194" s="35" t="s">
@@ -6399,7 +6428,7 @@
       <c r="E194" s="40"/>
       <c r="F194" s="43"/>
     </row>
-    <row r="195" ht="78" spans="1:6">
+    <row r="195" ht="88" spans="1:6">
       <c r="A195" s="47"/>
       <c r="B195" s="47"/>
       <c r="C195" s="35" t="s">
@@ -6411,7 +6440,7 @@
       <c r="E195" s="40"/>
       <c r="F195" s="43"/>
     </row>
-    <row r="196" ht="15.6" spans="1:6">
+    <row r="196" ht="18" spans="1:6">
       <c r="A196" s="47"/>
       <c r="B196" s="47"/>
       <c r="C196" s="35" t="s">
@@ -6423,7 +6452,7 @@
       <c r="E196" s="40"/>
       <c r="F196" s="43"/>
     </row>
-    <row r="197" ht="234" spans="1:6">
+    <row r="197" ht="282" spans="1:6">
       <c r="A197" s="47"/>
       <c r="B197" s="47"/>
       <c r="C197" s="35" t="s">
@@ -6447,7 +6476,7 @@
       <c r="E198" s="17"/>
       <c r="F198" s="18"/>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" ht="17" spans="1:6">
       <c r="A199" s="4" t="s">
         <v>1</v>
       </c>
@@ -6467,7 +6496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" ht="28.8" spans="1:6">
+    <row r="200" ht="34" spans="1:6">
       <c r="A200" s="5">
         <v>1</v>
       </c>
@@ -6483,7 +6512,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" ht="17" spans="1:6">
       <c r="A201" s="19"/>
       <c r="B201" s="20" t="s">
         <v>66</v>
@@ -6501,7 +6530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" ht="15.6" spans="1:6">
+    <row r="202" ht="18" spans="1:6">
       <c r="A202" s="47">
         <v>1</v>
       </c>
@@ -6517,7 +6546,7 @@
       <c r="E202" s="40"/>
       <c r="F202" s="43"/>
     </row>
-    <row r="203" ht="15.6" spans="1:6">
+    <row r="203" ht="18" spans="1:6">
       <c r="A203" s="47"/>
       <c r="B203" s="47"/>
       <c r="C203" s="35" t="s">
@@ -6529,7 +6558,7 @@
       <c r="E203" s="40"/>
       <c r="F203" s="43"/>
     </row>
-    <row r="204" ht="93.6" spans="1:6">
+    <row r="204" ht="106" spans="1:6">
       <c r="A204" s="47"/>
       <c r="B204" s="47"/>
       <c r="C204" s="35" t="s">
@@ -6541,7 +6570,7 @@
       <c r="E204" s="40"/>
       <c r="F204" s="43"/>
     </row>
-    <row r="205" ht="15.6" spans="1:6">
+    <row r="205" ht="17.6" spans="1:6">
       <c r="A205" s="47"/>
       <c r="B205" s="47"/>
       <c r="C205" s="48" t="s">
@@ -6553,7 +6582,7 @@
       <c r="E205" s="40"/>
       <c r="F205" s="43"/>
     </row>
-    <row r="206" ht="144" spans="1:6">
+    <row r="206" ht="185" spans="1:6">
       <c r="A206" s="47"/>
       <c r="B206" s="47"/>
       <c r="C206" s="49" t="s">
@@ -6575,7 +6604,7 @@
       <c r="E207" s="17"/>
       <c r="F207" s="18"/>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" ht="17" spans="1:6">
       <c r="A208" s="4" t="s">
         <v>1</v>
       </c>
@@ -6595,7 +6624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" ht="28.8" spans="1:6">
+    <row r="209" ht="34" spans="1:6">
       <c r="A209" s="5">
         <v>1</v>
       </c>
@@ -6611,7 +6640,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" ht="17" spans="1:6">
       <c r="A210" s="19"/>
       <c r="B210" s="20" t="s">
         <v>66</v>
@@ -6629,7 +6658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" ht="31.2" spans="1:6">
+    <row r="211" ht="53" spans="1:6">
       <c r="A211" s="47">
         <v>1</v>
       </c>
@@ -6645,7 +6674,7 @@
       <c r="E211" s="40"/>
       <c r="F211" s="43"/>
     </row>
-    <row r="212" ht="15.6" spans="1:6">
+    <row r="212" ht="18" spans="1:6">
       <c r="A212" s="47"/>
       <c r="B212" s="47"/>
       <c r="C212" s="35" t="s">
@@ -6657,7 +6686,7 @@
       <c r="E212" s="40"/>
       <c r="F212" s="43"/>
     </row>
-    <row r="213" ht="31.2" spans="1:6">
+    <row r="213" ht="36" spans="1:6">
       <c r="A213" s="47"/>
       <c r="B213" s="47"/>
       <c r="C213" s="35" t="s">
@@ -6669,7 +6698,7 @@
       <c r="E213" s="40"/>
       <c r="F213" s="43"/>
     </row>
-    <row r="214" ht="62.4" spans="1:6">
+    <row r="214" ht="71" spans="1:6">
       <c r="A214" s="47"/>
       <c r="B214" s="47"/>
       <c r="C214" s="35" t="s">
@@ -6681,7 +6710,7 @@
       <c r="E214" s="40"/>
       <c r="F214" s="43"/>
     </row>
-    <row r="215" ht="62.4" spans="1:6">
+    <row r="215" ht="71" spans="1:6">
       <c r="A215" s="47"/>
       <c r="B215" s="47"/>
       <c r="C215" s="35" t="s">
@@ -6693,7 +6722,7 @@
       <c r="E215" s="40"/>
       <c r="F215" s="43"/>
     </row>
-    <row r="216" ht="15.6" spans="1:6">
+    <row r="216" ht="17.6" spans="1:6">
       <c r="A216" s="47"/>
       <c r="B216" s="47"/>
       <c r="C216" s="48" t="s">
@@ -6705,7 +6734,7 @@
       <c r="E216" s="40"/>
       <c r="F216" s="43"/>
     </row>
-    <row r="217" ht="158.4" spans="1:6">
+    <row r="217" ht="185" spans="1:6">
       <c r="A217" s="47"/>
       <c r="B217" s="47"/>
       <c r="C217" s="49" t="s">
@@ -6747,7 +6776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" ht="86.4" spans="1:6">
+    <row r="220" ht="101" spans="1:6">
       <c r="A220" s="5">
         <v>1</v>
       </c>
@@ -6781,14 +6810,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" ht="28.8" spans="1:6">
+    <row r="222" ht="34" spans="1:6">
       <c r="A222" s="34">
         <v>1</v>
       </c>
       <c r="B222" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="C222" s="58" t="s">
+      <c r="C222" s="64" t="s">
         <v>223</v>
       </c>
       <c r="D222" s="44" t="s">
@@ -6797,7 +6826,7 @@
       <c r="E222" s="40"/>
       <c r="F222" s="43"/>
     </row>
-    <row r="223" ht="43.2" spans="1:6">
+    <row r="223" ht="51" spans="1:6">
       <c r="A223" s="37"/>
       <c r="B223" s="37"/>
       <c r="C223" s="38" t="s">
@@ -6828,7 +6857,7 @@
       <c r="B225" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="C225" s="58" t="s">
+      <c r="C225" s="64" t="s">
         <v>223</v>
       </c>
       <c r="D225" s="44" t="s">
@@ -6837,7 +6866,7 @@
       <c r="E225" s="40"/>
       <c r="F225" s="43"/>
     </row>
-    <row r="226" ht="43.2" spans="1:6">
+    <row r="226" ht="51" spans="1:6">
       <c r="A226" s="37"/>
       <c r="B226" s="37"/>
       <c r="C226" s="38" t="s">
@@ -6861,14 +6890,14 @@
       <c r="E227" s="40"/>
       <c r="F227" s="43"/>
     </row>
-    <row r="228" ht="28.8" spans="1:6">
+    <row r="228" ht="34" spans="1:6">
       <c r="A228" s="34">
         <v>3</v>
       </c>
       <c r="B228" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="58" t="s">
+      <c r="C228" s="64" t="s">
         <v>228</v>
       </c>
       <c r="D228" s="44" t="s">
@@ -6877,7 +6906,7 @@
       <c r="E228" s="40"/>
       <c r="F228" s="43"/>
     </row>
-    <row r="229" ht="28.8" spans="1:6">
+    <row r="229" ht="34" spans="1:6">
       <c r="A229" s="37"/>
       <c r="B229" s="37"/>
       <c r="C229" s="38" t="s">
@@ -6911,7 +6940,7 @@
       <c r="E231" s="17"/>
       <c r="F231" s="18"/>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" ht="17" spans="1:6">
       <c r="A232" s="4" t="s">
         <v>1</v>
       </c>
@@ -6931,7 +6960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" ht="28.8" spans="1:6">
+    <row r="233" ht="34" spans="1:6">
       <c r="A233" s="5">
         <v>1</v>
       </c>
@@ -6947,7 +6976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" ht="17" spans="1:6">
       <c r="A234" s="19"/>
       <c r="B234" s="20" t="s">
         <v>66</v>
@@ -6965,14 +6994,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" ht="15.6" spans="1:6">
+    <row r="235" ht="34" spans="1:6">
       <c r="A235" s="47">
         <v>1</v>
       </c>
       <c r="B235" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="C235" s="58" t="s">
+      <c r="C235" s="64" t="s">
         <v>232</v>
       </c>
       <c r="D235" s="44" t="s">
@@ -6981,7 +7010,7 @@
       <c r="E235" s="40"/>
       <c r="F235" s="43"/>
     </row>
-    <row r="236" ht="218.4" spans="1:6">
+    <row r="236" ht="247" spans="1:6">
       <c r="A236" s="47"/>
       <c r="B236" s="47"/>
       <c r="C236" s="38" t="s">
@@ -6995,7 +7024,7 @@
       </c>
       <c r="F236" s="43"/>
     </row>
-    <row r="237" ht="15.6" spans="1:6">
+    <row r="237" ht="18" spans="1:6">
       <c r="A237" s="47">
         <v>2</v>
       </c>
@@ -7011,10 +7040,10 @@
       <c r="E237" s="40"/>
       <c r="F237" s="43"/>
     </row>
-    <row r="238" ht="28.8" spans="1:6">
+    <row r="238" ht="34" spans="1:6">
       <c r="A238" s="47"/>
       <c r="B238" s="47"/>
-      <c r="C238" s="58" t="s">
+      <c r="C238" s="64" t="s">
         <v>237</v>
       </c>
       <c r="D238" s="44" t="s">
@@ -7023,7 +7052,7 @@
       <c r="E238" s="40"/>
       <c r="F238" s="43"/>
     </row>
-    <row r="239" ht="15.6" spans="1:6">
+    <row r="239" ht="17.6" spans="1:6">
       <c r="A239" s="47"/>
       <c r="B239" s="47"/>
       <c r="C239" s="38" t="s">
@@ -7035,7 +7064,7 @@
       <c r="E239" s="40"/>
       <c r="F239" s="43"/>
     </row>
-    <row r="240" ht="93.6" spans="1:6">
+    <row r="240" ht="106" spans="1:6">
       <c r="A240" s="47"/>
       <c r="B240" s="47"/>
       <c r="C240" s="35" t="s">
@@ -7049,7 +7078,7 @@
       </c>
       <c r="F240" s="43"/>
     </row>
-    <row r="241" ht="15.6" spans="1:6">
+    <row r="241" ht="18" spans="1:6">
       <c r="A241" s="47">
         <v>3</v>
       </c>
@@ -7065,7 +7094,7 @@
       <c r="E241" s="40"/>
       <c r="F241" s="43"/>
     </row>
-    <row r="242" ht="86.4" spans="1:6">
+    <row r="242" ht="118" spans="1:6">
       <c r="A242" s="47"/>
       <c r="B242" s="47"/>
       <c r="C242" s="38" t="s">
@@ -7077,7 +7106,7 @@
       <c r="E242" s="40"/>
       <c r="F242" s="43"/>
     </row>
-    <row r="243" ht="43.2" spans="1:6">
+    <row r="243" ht="51" spans="1:6">
       <c r="A243" s="47"/>
       <c r="B243" s="47"/>
       <c r="C243" s="49" t="s">
@@ -7089,7 +7118,7 @@
       <c r="E243" s="40"/>
       <c r="F243" s="43"/>
     </row>
-    <row r="244" ht="115.2" spans="1:6">
+    <row r="244" ht="135" spans="1:6">
       <c r="A244" s="47"/>
       <c r="B244" s="47"/>
       <c r="C244" s="49" t="s">
@@ -7101,11 +7130,11 @@
       <c r="E244" s="48"/>
       <c r="F244" s="48"/>
     </row>
-    <row r="245" ht="28.8" spans="1:6">
-      <c r="A245" s="59">
+    <row r="245" ht="34" spans="1:6">
+      <c r="A245" s="65">
         <v>4</v>
       </c>
-      <c r="B245" s="59" t="s">
+      <c r="B245" s="65" t="s">
         <v>246</v>
       </c>
       <c r="C245" s="49" t="s">
@@ -7117,9 +7146,9 @@
       <c r="E245" s="48"/>
       <c r="F245" s="48"/>
     </row>
-    <row r="246" ht="28.8" spans="1:6">
-      <c r="A246" s="59"/>
-      <c r="B246" s="59"/>
+    <row r="246" ht="51" spans="1:6">
+      <c r="A246" s="65"/>
+      <c r="B246" s="65"/>
       <c r="C246" s="49" t="s">
         <v>248</v>
       </c>
@@ -7129,9 +7158,9 @@
       <c r="E246" s="48"/>
       <c r="F246" s="48"/>
     </row>
-    <row r="247" ht="100.8" spans="1:6">
-      <c r="A247" s="59"/>
-      <c r="B247" s="59"/>
+    <row r="247" ht="135" spans="1:6">
+      <c r="A247" s="65"/>
+      <c r="B247" s="65"/>
       <c r="C247" s="49" t="s">
         <v>249</v>
       </c>
@@ -7153,7 +7182,7 @@
       <c r="E248" s="17"/>
       <c r="F248" s="18"/>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" ht="17" spans="1:6">
       <c r="A249" s="4" t="s">
         <v>1</v>
       </c>
@@ -7173,7 +7202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" ht="28.8" spans="1:6">
+    <row r="250" ht="34" spans="1:6">
       <c r="A250" s="5">
         <v>1</v>
       </c>
@@ -7189,7 +7218,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" ht="17" spans="1:6">
       <c r="A251" s="19"/>
       <c r="B251" s="20" t="s">
         <v>66</v>
@@ -7207,7 +7236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" ht="43.2" spans="1:6">
+    <row r="252" ht="51" spans="1:6">
       <c r="A252" s="47">
         <v>1</v>
       </c>
@@ -7225,7 +7254,7 @@
       </c>
       <c r="F252" s="43"/>
     </row>
-    <row r="253" ht="31.2" spans="1:6">
+    <row r="253" ht="36" spans="1:6">
       <c r="A253" s="47"/>
       <c r="B253" s="47"/>
       <c r="C253" s="35" t="s">
@@ -7237,7 +7266,7 @@
       <c r="E253" s="26"/>
       <c r="F253" s="43"/>
     </row>
-    <row r="254" ht="28.8" spans="1:6">
+    <row r="254" ht="36" spans="1:6">
       <c r="A254" s="47"/>
       <c r="B254" s="47"/>
       <c r="C254" s="35" t="s">
@@ -7251,11 +7280,11 @@
       </c>
       <c r="F254" s="49"/>
     </row>
-    <row r="255" ht="31.2" spans="1:6">
-      <c r="A255" s="60">
+    <row r="255" ht="36" spans="1:6">
+      <c r="A255" s="66">
         <v>2</v>
       </c>
-      <c r="B255" s="60" t="s">
+      <c r="B255" s="66" t="s">
         <v>235</v>
       </c>
       <c r="C255" s="35" t="s">
@@ -7269,8 +7298,8 @@
         <v>252</v>
       </c>
     </row>
-    <row r="256" ht="31.2" spans="1:6">
-      <c r="A256" s="60"/>
+    <row r="256" ht="36" spans="1:6">
+      <c r="A256" s="66"/>
       <c r="B256" s="49"/>
       <c r="C256" s="35" t="s">
         <v>253</v>
@@ -7283,7 +7312,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="257" ht="31.2" spans="1:6">
+    <row r="257" ht="36" spans="1:6">
       <c r="A257" s="47">
         <v>3</v>
       </c>
@@ -7301,7 +7330,7 @@
       </c>
       <c r="F257" s="38"/>
     </row>
-    <row r="258" ht="31.2" spans="1:6">
+    <row r="258" ht="36" spans="1:6">
       <c r="A258" s="47"/>
       <c r="B258" s="47"/>
       <c r="C258" s="35" t="s">
@@ -7313,7 +7342,7 @@
       <c r="E258" s="47"/>
       <c r="F258" s="38"/>
     </row>
-    <row r="259" ht="15.6" spans="1:6">
+    <row r="259" ht="18" spans="1:6">
       <c r="A259" s="47"/>
       <c r="B259" s="47"/>
       <c r="C259" s="35" t="s">
@@ -7335,7 +7364,7 @@
       <c r="E260" s="17"/>
       <c r="F260" s="18"/>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" ht="17" spans="1:6">
       <c r="A261" s="4" t="s">
         <v>1</v>
       </c>
@@ -7355,7 +7384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="262" ht="28.8" spans="1:6">
+    <row r="262" ht="34" spans="1:6">
       <c r="A262" s="5">
         <v>1</v>
       </c>
@@ -7371,7 +7400,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" ht="17" spans="1:6">
       <c r="A263" s="19"/>
       <c r="B263" s="20" t="s">
         <v>66</v>
@@ -7389,7 +7418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" ht="43.2" spans="1:6">
+    <row r="264" ht="51" spans="1:6">
       <c r="A264" s="47">
         <v>1</v>
       </c>
@@ -7407,7 +7436,7 @@
       </c>
       <c r="F264" s="43"/>
     </row>
-    <row r="265" ht="31.2" spans="1:6">
+    <row r="265" ht="36" spans="1:6">
       <c r="A265" s="47"/>
       <c r="B265" s="47"/>
       <c r="C265" s="35" t="s">
@@ -7419,7 +7448,7 @@
       <c r="E265" s="26"/>
       <c r="F265" s="43"/>
     </row>
-    <row r="266" ht="28.8" spans="1:6">
+    <row r="266" ht="36" spans="1:6">
       <c r="A266" s="47"/>
       <c r="B266" s="47"/>
       <c r="C266" s="35" t="s">
@@ -7433,11 +7462,11 @@
       </c>
       <c r="F266" s="49"/>
     </row>
-    <row r="267" ht="46.8" spans="1:6">
-      <c r="A267" s="60">
+    <row r="267" ht="53" spans="1:6">
+      <c r="A267" s="66">
         <v>2</v>
       </c>
-      <c r="B267" s="60" t="s">
+      <c r="B267" s="66" t="s">
         <v>235</v>
       </c>
       <c r="C267" s="35" t="s">
@@ -7451,8 +7480,8 @@
         <v>255</v>
       </c>
     </row>
-    <row r="268" ht="46.8" spans="1:6">
-      <c r="A268" s="60"/>
+    <row r="268" ht="53" spans="1:6">
+      <c r="A268" s="66"/>
       <c r="B268" s="49"/>
       <c r="C268" s="35" t="s">
         <v>256</v>
@@ -7465,11 +7494,11 @@
         <v>255</v>
       </c>
     </row>
-    <row r="269" ht="62.4" spans="1:6">
+    <row r="269" ht="71" spans="1:6">
       <c r="A269" s="47">
         <v>3</v>
       </c>
-      <c r="B269" s="61" t="s">
+      <c r="B269" s="67" t="s">
         <v>143</v>
       </c>
       <c r="C269" s="35" t="s">
@@ -7608,14 +7637,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="45.4907407407407" customWidth="1"/>
-    <col min="4" max="4" width="56.8981481481481" customWidth="1"/>
-    <col min="5" max="5" width="30.8425925925926" customWidth="1"/>
-    <col min="6" max="6" width="42.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="11.8846153846154" customWidth="1"/>
+    <col min="2" max="2" width="18.6634615384615" customWidth="1"/>
+    <col min="3" max="3" width="45.4903846153846" customWidth="1"/>
+    <col min="4" max="4" width="56.8942307692308" customWidth="1"/>
+    <col min="5" max="5" width="30.8461538461538" customWidth="1"/>
+    <col min="6" max="6" width="42.3365384615385" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7628,7 +7657,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="17" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -7648,7 +7677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="17" spans="1:6">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -7664,7 +7693,7 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" ht="28.8" spans="1:6">
+    <row r="4" ht="34" spans="1:6">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -7680,7 +7709,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" ht="28.8" spans="1:6">
+    <row r="5" ht="34" spans="1:6">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -7696,7 +7725,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" ht="28.8" spans="1:6">
+    <row r="6" ht="34" spans="1:6">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -7712,7 +7741,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" ht="28.8" spans="1:6">
+    <row r="7" ht="34" spans="1:6">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -7738,7 +7767,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" ht="17" spans="1:6">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -7750,7 +7779,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" ht="17" spans="1:6">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -7762,7 +7791,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" ht="17" spans="1:6">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -7780,7 +7809,7 @@
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" ht="17" spans="1:6">
       <c r="A12" s="5">
         <v>4</v>
       </c>
@@ -7792,7 +7821,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" ht="17" spans="1:6">
       <c r="A13" s="5">
         <v>5</v>
       </c>
@@ -7808,7 +7837,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="10"/>
     </row>
-    <row r="14" ht="28.8" spans="1:6">
+    <row r="14" ht="34" spans="1:6">
       <c r="A14" s="5">
         <v>6</v>
       </c>
@@ -7824,7 +7853,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" ht="17" spans="1:6">
       <c r="A15" s="5">
         <v>7</v>
       </c>
@@ -7840,7 +7869,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
     </row>
-    <row r="16" ht="28.8" spans="1:6">
+    <row r="16" ht="34" spans="1:6">
       <c r="A16" s="5">
         <v>8</v>
       </c>
@@ -7856,7 +7885,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" ht="17" spans="1:6">
       <c r="A17" s="5">
         <v>9</v>
       </c>
@@ -7872,7 +7901,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="10"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" ht="17" spans="1:6">
       <c r="A18" s="5">
         <v>10</v>
       </c>
@@ -7898,7 +7927,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" ht="17" spans="1:6">
       <c r="A20" s="5">
         <v>1</v>
       </c>
@@ -7914,7 +7943,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" ht="34" spans="1:6">
       <c r="A21" s="5">
         <v>2</v>
       </c>
@@ -7930,7 +7959,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" ht="17" spans="1:6">
       <c r="A22" s="5">
         <v>3</v>
       </c>
@@ -7946,7 +7975,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" ht="17" spans="1:6">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -7962,7 +7991,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" ht="43.2" spans="1:6">
+    <row r="24" ht="51" spans="1:6">
       <c r="A24" s="5">
         <v>5</v>
       </c>
@@ -7990,7 +8019,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" ht="28.8" spans="1:6">
+    <row r="26" ht="34" spans="1:6">
       <c r="A26" s="5">
         <v>1</v>
       </c>
@@ -8008,7 +8037,7 @@
       </c>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" ht="72" spans="1:6">
+    <row r="27" ht="78" spans="1:6">
       <c r="A27" s="5">
         <v>2</v>
       </c>
@@ -8026,7 +8055,7 @@
       </c>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" ht="34" spans="1:6">
       <c r="A28" s="5">
         <v>3</v>
       </c>
@@ -8042,7 +8071,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" ht="17" spans="1:6">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -8084,7 +8113,7 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" ht="28.8" spans="1:6">
+    <row r="32" ht="34" spans="1:6">
       <c r="A32" s="5">
         <v>2</v>
       </c>
@@ -8110,7 +8139,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" ht="17" spans="1:6">
       <c r="A34" s="4" t="s">
         <v>1</v>
       </c>
@@ -8130,7 +8159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" ht="28.8" spans="1:6">
+    <row r="35" ht="34" spans="1:6">
       <c r="A35" s="5">
         <v>1</v>
       </c>
@@ -8146,7 +8175,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" ht="17" spans="1:6">
       <c r="A36" s="19"/>
       <c r="B36" s="20" t="s">
         <v>66</v>
@@ -8180,7 +8209,7 @@
       <c r="E37" s="11"/>
       <c r="F37" s="23"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" ht="17" spans="1:6">
       <c r="A38" s="24"/>
       <c r="B38" s="25"/>
       <c r="C38" s="11" t="s">
@@ -8204,7 +8233,7 @@
       <c r="E39" s="11"/>
       <c r="F39" s="23"/>
     </row>
-    <row r="40" ht="100.8" spans="1:6">
+    <row r="40" ht="118" spans="1:6">
       <c r="A40" s="24"/>
       <c r="B40" s="25"/>
       <c r="C40" s="11" t="s">
@@ -8218,7 +8247,7 @@
       </c>
       <c r="F40" s="23"/>
     </row>
-    <row r="41" ht="43.2" spans="1:6">
+    <row r="41" ht="51" spans="1:6">
       <c r="A41" s="24"/>
       <c r="B41" s="25"/>
       <c r="C41" s="26" t="s">
@@ -8230,7 +8259,7 @@
       <c r="E41" s="11"/>
       <c r="F41" s="23"/>
     </row>
-    <row r="42" ht="28.8" spans="1:6">
+    <row r="42" ht="34" spans="1:6">
       <c r="A42" s="24"/>
       <c r="B42" s="25"/>
       <c r="C42" s="26" t="s">
@@ -8242,7 +8271,7 @@
       <c r="E42" s="11"/>
       <c r="F42" s="23"/>
     </row>
-    <row r="43" ht="43.2" spans="1:6">
+    <row r="43" ht="51" spans="1:6">
       <c r="A43" s="24"/>
       <c r="B43" s="25"/>
       <c r="C43" s="26" t="s">
@@ -8254,7 +8283,7 @@
       <c r="E43" s="26"/>
       <c r="F43" s="23"/>
     </row>
-    <row r="44" ht="43.2" spans="1:6">
+    <row r="44" ht="68" spans="1:6">
       <c r="A44" s="24"/>
       <c r="B44" s="25"/>
       <c r="C44" s="26" t="s">
@@ -8266,7 +8295,7 @@
       <c r="E44" s="11"/>
       <c r="F44" s="23"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" ht="17" spans="1:6">
       <c r="A45" s="27"/>
       <c r="B45" s="28"/>
       <c r="C45" s="26" t="s">
@@ -8288,7 +8317,7 @@
       <c r="E46" s="17"/>
       <c r="F46" s="18"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" ht="17" spans="1:6">
       <c r="A47" s="4" t="s">
         <v>1</v>
       </c>
@@ -8308,7 +8337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" ht="28.8" spans="1:6">
+    <row r="48" ht="34" spans="1:6">
       <c r="A48" s="5">
         <v>1</v>
       </c>
@@ -8324,7 +8353,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" ht="17" spans="1:6">
       <c r="A49" s="19"/>
       <c r="B49" s="20" t="s">
         <v>66</v>
@@ -8370,7 +8399,7 @@
       <c r="E51" s="11"/>
       <c r="F51" s="23"/>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" ht="17" spans="1:6">
       <c r="A52" s="29"/>
       <c r="B52" s="30"/>
       <c r="C52" s="11" t="s">
@@ -8382,7 +8411,7 @@
       <c r="E52" s="11"/>
       <c r="F52" s="23"/>
     </row>
-    <row r="53" ht="57.6" spans="1:6">
+    <row r="53" ht="68" spans="1:6">
       <c r="A53" s="29"/>
       <c r="B53" s="30"/>
       <c r="C53" t="s">
@@ -8434,7 +8463,7 @@
       <c r="E56" s="11"/>
       <c r="F56" s="23"/>
     </row>
-    <row r="57" ht="28.8" spans="1:6">
+    <row r="57" ht="34" spans="1:6">
       <c r="A57" s="29"/>
       <c r="B57" s="30"/>
       <c r="C57" s="26" t="s">
@@ -8446,7 +8475,7 @@
       <c r="E57" s="11"/>
       <c r="F57" s="23"/>
     </row>
-    <row r="58" ht="28.8" spans="1:6">
+    <row r="58" ht="34" spans="1:6">
       <c r="A58" s="29"/>
       <c r="B58" s="30"/>
       <c r="C58" s="26" t="s">
@@ -8458,7 +8487,7 @@
       <c r="E58" s="11"/>
       <c r="F58" s="23"/>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" ht="17" spans="1:6">
       <c r="A59" s="29"/>
       <c r="B59" s="30"/>
       <c r="C59" s="26" t="s">
@@ -8482,7 +8511,7 @@
       <c r="E60" s="17"/>
       <c r="F60" s="18"/>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" ht="17" spans="1:6">
       <c r="A61" s="4" t="s">
         <v>1</v>
       </c>
@@ -8502,7 +8531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" ht="28.8" spans="1:6">
+    <row r="62" ht="34" spans="1:6">
       <c r="A62" s="5">
         <v>1</v>
       </c>
@@ -8518,7 +8547,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" ht="17" spans="1:6">
       <c r="A63" s="19"/>
       <c r="B63" s="20" t="s">
         <v>66</v>
@@ -8552,7 +8581,7 @@
       <c r="E64" s="11"/>
       <c r="F64" s="23"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" ht="17" spans="1:6">
       <c r="A65" s="29"/>
       <c r="B65" s="30"/>
       <c r="C65" s="11" t="s">
@@ -8588,7 +8617,7 @@
       <c r="E67" s="11"/>
       <c r="F67" s="32"/>
     </row>
-    <row r="68" ht="115.2" spans="1:6">
+    <row r="68" ht="152" spans="1:6">
       <c r="A68" s="29"/>
       <c r="B68" s="30"/>
       <c r="C68" s="11" t="s">
@@ -8626,7 +8655,7 @@
       <c r="E70" s="11"/>
       <c r="F70" s="32"/>
     </row>
-    <row r="71" ht="28.8" spans="1:6">
+    <row r="71" ht="34" spans="1:6">
       <c r="A71" s="29"/>
       <c r="B71" s="30"/>
       <c r="C71" s="26" t="s">
@@ -8638,7 +8667,7 @@
       <c r="E71" s="11"/>
       <c r="F71" s="32"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" ht="17" spans="1:6">
       <c r="A72" s="29"/>
       <c r="B72" s="30"/>
       <c r="C72" s="26" t="s">
@@ -8662,7 +8691,7 @@
       <c r="E73" s="17"/>
       <c r="F73" s="18"/>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" ht="17" spans="1:6">
       <c r="A74" s="4" t="s">
         <v>1</v>
       </c>
@@ -8682,7 +8711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" ht="28.8" spans="1:6">
+    <row r="75" ht="34" spans="1:6">
       <c r="A75" s="5">
         <v>1</v>
       </c>
@@ -8698,7 +8727,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" ht="17" spans="1:6">
       <c r="A76" s="19"/>
       <c r="B76" s="20" t="s">
         <v>66</v>
@@ -8744,7 +8773,7 @@
       <c r="E78" s="11"/>
       <c r="F78" s="23"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" ht="17" spans="1:6">
       <c r="A79" s="29"/>
       <c r="B79" s="30"/>
       <c r="C79" s="11" t="s">
@@ -8778,7 +8807,7 @@
       <c r="E81" s="31"/>
       <c r="F81" s="23"/>
     </row>
-    <row r="82" ht="28.8" spans="1:6">
+    <row r="82" ht="34" spans="1:6">
       <c r="A82" s="29"/>
       <c r="B82" s="30"/>
       <c r="C82" s="26" t="s">
@@ -8788,7 +8817,7 @@
       <c r="E82" s="11"/>
       <c r="F82" s="32"/>
     </row>
-    <row r="83" ht="86.4" spans="1:6">
+    <row r="83" ht="101" spans="1:6">
       <c r="A83" s="29"/>
       <c r="B83" s="30"/>
       <c r="C83" s="26" t="s">
@@ -8800,7 +8829,7 @@
       <c r="E83" s="11"/>
       <c r="F83" s="32"/>
     </row>
-    <row r="84" ht="100.8" spans="1:6">
+    <row r="84" ht="118" spans="1:6">
       <c r="A84" s="29"/>
       <c r="B84" s="30"/>
       <c r="C84" s="26" t="s">
@@ -8838,7 +8867,7 @@
       </c>
       <c r="F86" s="32"/>
     </row>
-    <row r="87" ht="28.8" spans="1:6">
+    <row r="87" ht="34" spans="1:6">
       <c r="A87" s="29"/>
       <c r="B87" s="30"/>
       <c r="C87" s="26" t="s">
@@ -8850,7 +8879,7 @@
       <c r="E87" s="11"/>
       <c r="F87" s="32"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" ht="17" spans="1:6">
       <c r="A88" s="29"/>
       <c r="B88" s="30"/>
       <c r="C88" s="26" t="s">
@@ -8874,7 +8903,7 @@
       <c r="E89" s="17"/>
       <c r="F89" s="18"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" ht="17" spans="1:6">
       <c r="A90" s="4" t="s">
         <v>1</v>
       </c>
@@ -8894,7 +8923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" ht="100.8" spans="1:6">
+    <row r="91" ht="135" spans="1:6">
       <c r="A91" s="5">
         <v>1</v>
       </c>
@@ -8912,7 +8941,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" ht="17" spans="1:6">
       <c r="A92" s="19"/>
       <c r="B92" s="20" t="s">
         <v>66</v>
@@ -8930,7 +8959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" ht="78" spans="1:6">
+    <row r="93" ht="106" spans="1:6">
       <c r="A93" s="34">
         <v>1</v>
       </c>
@@ -8946,7 +8975,7 @@
       <c r="E93" s="26"/>
       <c r="F93" s="36"/>
     </row>
-    <row r="94" ht="78" spans="1:6">
+    <row r="94" ht="88" spans="1:6">
       <c r="A94" s="37"/>
       <c r="B94" s="37"/>
       <c r="C94" s="35" t="s">
@@ -8958,7 +8987,7 @@
       <c r="E94" s="11"/>
       <c r="F94" s="36"/>
     </row>
-    <row r="95" ht="43.2" spans="1:6">
+    <row r="95" ht="51" spans="1:6">
       <c r="A95" s="37"/>
       <c r="B95" s="37"/>
       <c r="C95" s="35" t="s">
@@ -8970,7 +8999,7 @@
       </c>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" ht="86.4" spans="1:6">
+    <row r="96" ht="101" spans="1:6">
       <c r="A96" s="37"/>
       <c r="B96" s="37"/>
       <c r="C96" s="26" t="s">
@@ -8982,7 +9011,7 @@
       <c r="E96" s="38"/>
       <c r="F96" s="36"/>
     </row>
-    <row r="97" ht="86.4" spans="1:6">
+    <row r="97" ht="101" spans="1:6">
       <c r="A97" s="37"/>
       <c r="B97" s="37"/>
       <c r="C97" s="26" t="s">
@@ -8994,7 +9023,7 @@
       <c r="E97" s="39"/>
       <c r="F97" s="36"/>
     </row>
-    <row r="98" ht="15.6" spans="1:6">
+    <row r="98" ht="17.6" spans="1:6">
       <c r="A98" s="37"/>
       <c r="B98" s="37"/>
       <c r="C98" s="11" t="s">
@@ -9006,7 +9035,7 @@
       <c r="E98" s="40"/>
       <c r="F98" s="36"/>
     </row>
-    <row r="99" ht="28.8" spans="1:6">
+    <row r="99" ht="34" spans="1:6">
       <c r="A99" s="37"/>
       <c r="B99" s="37"/>
       <c r="C99" s="26" t="s">
@@ -9018,7 +9047,7 @@
       <c r="E99" s="40"/>
       <c r="F99" s="36"/>
     </row>
-    <row r="100" ht="15.6" spans="1:6">
+    <row r="100" ht="17.6" spans="1:6">
       <c r="A100" s="37"/>
       <c r="B100" s="37"/>
       <c r="C100" s="11" t="s">
@@ -9030,7 +9059,7 @@
       <c r="E100" s="40"/>
       <c r="F100" s="36"/>
     </row>
-    <row r="101" ht="78" spans="1:6">
+    <row r="101" ht="88" spans="1:6">
       <c r="A101" s="37"/>
       <c r="B101" s="37"/>
       <c r="C101" s="35" t="s">
@@ -9042,7 +9071,7 @@
       <c r="E101" s="40"/>
       <c r="F101" s="36"/>
     </row>
-    <row r="102" ht="15.6" spans="1:6">
+    <row r="102" ht="18" spans="1:6">
       <c r="A102" s="37"/>
       <c r="B102" s="37"/>
       <c r="C102" s="35" t="s">
@@ -9054,7 +9083,7 @@
       <c r="E102" s="40"/>
       <c r="F102" s="36"/>
     </row>
-    <row r="103" ht="15.6" spans="1:6">
+    <row r="103" ht="18" spans="1:6">
       <c r="A103" s="41"/>
       <c r="B103" s="41"/>
       <c r="C103" s="35" t="s">
@@ -9076,7 +9105,7 @@
       <c r="E104" s="17"/>
       <c r="F104" s="18"/>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" ht="17" spans="1:6">
       <c r="A105" s="4" t="s">
         <v>1</v>
       </c>
@@ -9096,7 +9125,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" ht="28.8" spans="1:6">
+    <row r="106" ht="34" spans="1:6">
       <c r="A106" s="5">
         <v>1</v>
       </c>
@@ -9112,7 +9141,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" ht="17" spans="1:6">
       <c r="A107" s="19"/>
       <c r="B107" s="20" t="s">
         <v>66</v>
@@ -9130,7 +9159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" ht="46.8" spans="1:6">
+    <row r="108" ht="53" spans="1:6">
       <c r="A108" s="34">
         <v>1</v>
       </c>
@@ -9148,7 +9177,7 @@
       </c>
       <c r="F108" s="36"/>
     </row>
-    <row r="109" ht="15.6" spans="1:6">
+    <row r="109" ht="17.6" spans="1:6">
       <c r="A109" s="37"/>
       <c r="B109" s="37"/>
       <c r="C109" s="11" t="s">
@@ -9160,7 +9189,7 @@
       <c r="E109" s="40"/>
       <c r="F109" s="36"/>
     </row>
-    <row r="110" ht="218.4" spans="1:6">
+    <row r="110" ht="247" spans="1:6">
       <c r="A110" s="37"/>
       <c r="B110" s="37"/>
       <c r="C110" s="26" t="s">
@@ -9174,7 +9203,7 @@
       </c>
       <c r="F110" s="36"/>
     </row>
-    <row r="111" ht="115.2" spans="1:6">
+    <row r="111" ht="135" spans="1:6">
       <c r="A111" s="37"/>
       <c r="B111" s="37"/>
       <c r="C111" s="26" t="s">
@@ -9186,7 +9215,7 @@
       <c r="E111" s="40"/>
       <c r="F111" s="36"/>
     </row>
-    <row r="112" ht="249.6" spans="1:6">
+    <row r="112" ht="282" spans="1:6">
       <c r="A112" s="37"/>
       <c r="B112" s="37"/>
       <c r="C112" s="35" t="s">
@@ -9200,7 +9229,7 @@
       </c>
       <c r="F112" s="36"/>
     </row>
-    <row r="113" ht="15.6" spans="1:6">
+    <row r="113" ht="17.6" spans="1:6">
       <c r="A113" s="37"/>
       <c r="B113" s="37"/>
       <c r="C113" s="11" t="s">
@@ -9212,7 +9241,7 @@
       <c r="E113" s="40"/>
       <c r="F113" s="36"/>
     </row>
-    <row r="114" ht="156" spans="1:6">
+    <row r="114" ht="176" spans="1:6">
       <c r="A114" s="37"/>
       <c r="B114" s="37"/>
       <c r="C114" s="35" t="s">
@@ -9224,7 +9253,7 @@
       <c r="E114" s="40"/>
       <c r="F114" s="36"/>
     </row>
-    <row r="115" ht="93.6" spans="1:6">
+    <row r="115" ht="106" spans="1:6">
       <c r="A115" s="37"/>
       <c r="B115" s="37"/>
       <c r="C115" s="35" t="s">
@@ -9236,7 +9265,7 @@
       <c r="E115" s="40"/>
       <c r="F115" s="36"/>
     </row>
-    <row r="116" ht="72" spans="1:6">
+    <row r="116" ht="84" spans="1:6">
       <c r="A116" s="37"/>
       <c r="B116" s="37"/>
       <c r="C116" s="42" t="s">
@@ -9248,7 +9277,7 @@
       <c r="E116" s="40"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="117" ht="78" spans="1:6">
+    <row r="117" ht="88" spans="1:6">
       <c r="A117" s="37"/>
       <c r="B117" s="37"/>
       <c r="C117" s="35" t="s">
@@ -9260,7 +9289,7 @@
       <c r="E117" s="40"/>
       <c r="F117" s="36"/>
     </row>
-    <row r="118" ht="156" spans="1:6">
+    <row r="118" ht="194" spans="1:6">
       <c r="A118" s="37"/>
       <c r="B118" s="37"/>
       <c r="C118" s="35" t="s">
@@ -9272,7 +9301,7 @@
       <c r="E118" s="40"/>
       <c r="F118" s="36"/>
     </row>
-    <row r="119" ht="93.6" spans="1:6">
+    <row r="119" ht="106" spans="1:6">
       <c r="A119" s="37"/>
       <c r="B119" s="37"/>
       <c r="C119" s="35" t="s">
@@ -9284,7 +9313,7 @@
       <c r="E119" s="40"/>
       <c r="F119" s="36"/>
     </row>
-    <row r="120" ht="15.6" spans="1:6">
+    <row r="120" ht="17.6" spans="1:6">
       <c r="A120" s="37"/>
       <c r="B120" s="37"/>
       <c r="C120" s="11" t="s">
@@ -9296,7 +9325,7 @@
       <c r="E120" s="40"/>
       <c r="F120" s="36"/>
     </row>
-    <row r="121" ht="15.6" spans="1:6">
+    <row r="121" ht="18" spans="1:6">
       <c r="A121" s="37"/>
       <c r="B121" s="37"/>
       <c r="C121" s="35" t="s">
@@ -9308,7 +9337,7 @@
       <c r="E121" s="40"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="122" ht="72" spans="1:6">
+    <row r="122" ht="84" spans="1:6">
       <c r="A122" s="37"/>
       <c r="B122" s="37"/>
       <c r="C122" s="26" t="s">
@@ -9320,7 +9349,7 @@
       <c r="E122" s="40"/>
       <c r="F122" s="36"/>
     </row>
-    <row r="123" ht="43.2" spans="1:6">
+    <row r="123" ht="68" spans="1:6">
       <c r="A123" s="37"/>
       <c r="B123" s="37"/>
       <c r="C123" s="26" t="s">
@@ -9332,7 +9361,7 @@
       <c r="E123" s="40"/>
       <c r="F123" s="36"/>
     </row>
-    <row r="124" ht="28.8" spans="1:6">
+    <row r="124" ht="34" spans="1:6">
       <c r="A124" s="37"/>
       <c r="B124" s="37"/>
       <c r="C124" s="26" t="s">
@@ -9344,7 +9373,7 @@
       <c r="E124" s="40"/>
       <c r="F124" s="36"/>
     </row>
-    <row r="125" ht="15.6" spans="1:6">
+    <row r="125" ht="18" spans="1:6">
       <c r="A125" s="37"/>
       <c r="B125" s="37"/>
       <c r="C125" s="35" t="s">
@@ -9356,7 +9385,7 @@
       <c r="E125" s="40"/>
       <c r="F125" s="36"/>
     </row>
-    <row r="126" ht="302.4" spans="1:6">
+    <row r="126" ht="387" spans="1:6">
       <c r="A126" s="41"/>
       <c r="B126" s="41"/>
       <c r="C126" s="26" t="s">
@@ -9380,7 +9409,7 @@
       <c r="E127" s="17"/>
       <c r="F127" s="18"/>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" ht="17" spans="1:6">
       <c r="A128" s="4" t="s">
         <v>1</v>
       </c>
@@ -9400,7 +9429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" ht="28.8" spans="1:6">
+    <row r="129" ht="34" spans="1:6">
       <c r="A129" s="5">
         <v>1</v>
       </c>
@@ -9416,7 +9445,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" ht="17" spans="1:6">
       <c r="A130" s="19"/>
       <c r="B130" s="20" t="s">
         <v>66</v>
@@ -9434,7 +9463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" ht="46.8" spans="1:6">
+    <row r="131" ht="53" spans="1:6">
       <c r="A131" s="34">
         <v>1</v>
       </c>
@@ -9452,7 +9481,7 @@
       </c>
       <c r="F131" s="43"/>
     </row>
-    <row r="132" ht="15.6" spans="1:6">
+    <row r="132" ht="17.6" spans="1:6">
       <c r="A132" s="37"/>
       <c r="B132" s="37"/>
       <c r="C132" s="11" t="s">
@@ -9464,7 +9493,7 @@
       <c r="E132" s="40"/>
       <c r="F132" s="43"/>
     </row>
-    <row r="133" ht="218.4" spans="1:6">
+    <row r="133" ht="247" spans="1:6">
       <c r="A133" s="37"/>
       <c r="B133" s="37"/>
       <c r="C133" s="26" t="s">
@@ -9478,7 +9507,7 @@
       </c>
       <c r="F133" s="43"/>
     </row>
-    <row r="134" ht="115.2" spans="1:6">
+    <row r="134" ht="135" spans="1:6">
       <c r="A134" s="37"/>
       <c r="B134" s="37"/>
       <c r="C134" s="26" t="s">
@@ -9490,7 +9519,7 @@
       <c r="E134" s="40"/>
       <c r="F134" s="43"/>
     </row>
-    <row r="135" ht="244.8" spans="1:6">
+    <row r="135" ht="303" spans="1:6">
       <c r="A135" s="37"/>
       <c r="B135" s="37"/>
       <c r="C135" s="26" t="s">
@@ -9502,7 +9531,7 @@
       <c r="E135" s="40"/>
       <c r="F135" s="43"/>
     </row>
-    <row r="136" ht="46.8" spans="1:6">
+    <row r="136" ht="53" spans="1:6">
       <c r="A136" s="37"/>
       <c r="B136" s="37"/>
       <c r="C136" s="39" t="s">
@@ -9514,7 +9543,7 @@
       <c r="E136" s="40"/>
       <c r="F136" s="43"/>
     </row>
-    <row r="137" ht="15.6" spans="1:6">
+    <row r="137" ht="17.6" spans="1:6">
       <c r="A137" s="37"/>
       <c r="B137" s="37"/>
       <c r="C137" s="11" t="s">
@@ -9526,7 +9555,7 @@
       <c r="E137" s="40"/>
       <c r="F137" s="43"/>
     </row>
-    <row r="138" ht="187.2" spans="1:6">
+    <row r="138" ht="212" spans="1:6">
       <c r="A138" s="37"/>
       <c r="B138" s="37"/>
       <c r="C138" s="44" t="s">
@@ -9540,7 +9569,7 @@
       </c>
       <c r="F138" s="43"/>
     </row>
-    <row r="139" ht="72" spans="1:6">
+    <row r="139" ht="101" spans="1:6">
       <c r="A139" s="37"/>
       <c r="B139" s="37"/>
       <c r="C139" s="44" t="s">
@@ -9552,7 +9581,7 @@
       <c r="E139" s="40"/>
       <c r="F139" s="43"/>
     </row>
-    <row r="140" ht="57.6" spans="1:6">
+    <row r="140" ht="101" spans="1:6">
       <c r="A140" s="37"/>
       <c r="B140" s="37"/>
       <c r="C140" s="44" t="s">
@@ -9564,7 +9593,7 @@
       <c r="E140" s="40"/>
       <c r="F140" s="43"/>
     </row>
-    <row r="141" ht="62.4" spans="1:6">
+    <row r="141" ht="71" spans="1:6">
       <c r="A141" s="37"/>
       <c r="B141" s="37"/>
       <c r="C141" s="35" t="s">
@@ -9576,7 +9605,7 @@
       <c r="E141" s="40"/>
       <c r="F141" s="43"/>
     </row>
-    <row r="142" ht="156" spans="1:6">
+    <row r="142" ht="194" spans="1:6">
       <c r="A142" s="37"/>
       <c r="B142" s="37"/>
       <c r="C142" s="35" t="s">
@@ -9588,7 +9617,7 @@
       <c r="E142" s="40"/>
       <c r="F142" s="43"/>
     </row>
-    <row r="143" ht="93.6" spans="1:6">
+    <row r="143" ht="106" spans="1:6">
       <c r="A143" s="37"/>
       <c r="B143" s="37"/>
       <c r="C143" s="35" t="s">
@@ -9600,7 +9629,7 @@
       <c r="E143" s="40"/>
       <c r="F143" s="43"/>
     </row>
-    <row r="144" ht="15.6" spans="1:6">
+    <row r="144" ht="17.6" spans="1:6">
       <c r="A144" s="37"/>
       <c r="B144" s="37"/>
       <c r="C144" s="11" t="s">
@@ -9612,7 +9641,7 @@
       <c r="E144" s="40"/>
       <c r="F144" s="43"/>
     </row>
-    <row r="145" ht="86.4" spans="1:6">
+    <row r="145" ht="101" spans="1:6">
       <c r="A145" s="37"/>
       <c r="B145" s="37"/>
       <c r="C145" s="26" t="s">
@@ -9624,7 +9653,7 @@
       <c r="E145" s="40"/>
       <c r="F145" s="43"/>
     </row>
-    <row r="146" ht="72" spans="1:6">
+    <row r="146" ht="84" spans="1:6">
       <c r="A146" s="37"/>
       <c r="B146" s="37"/>
       <c r="C146" s="26" t="s">
@@ -9636,7 +9665,7 @@
       <c r="E146" s="40"/>
       <c r="F146" s="43"/>
     </row>
-    <row r="147" ht="43.2" spans="1:6">
+    <row r="147" ht="68" spans="1:6">
       <c r="A147" s="37"/>
       <c r="B147" s="37"/>
       <c r="C147" s="26" t="s">
@@ -9648,7 +9677,7 @@
       <c r="E147" s="40"/>
       <c r="F147" s="43"/>
     </row>
-    <row r="148" ht="28.8" spans="1:6">
+    <row r="148" ht="34" spans="1:6">
       <c r="A148" s="37"/>
       <c r="B148" s="37"/>
       <c r="C148" s="26" t="s">
@@ -9660,7 +9689,7 @@
       <c r="E148" s="40"/>
       <c r="F148" s="43"/>
     </row>
-    <row r="149" ht="15.6" spans="1:6">
+    <row r="149" ht="18" spans="1:6">
       <c r="A149" s="37"/>
       <c r="B149" s="37"/>
       <c r="C149" s="35" t="s">
@@ -9672,7 +9701,7 @@
       <c r="E149" s="40"/>
       <c r="F149" s="43"/>
     </row>
-    <row r="150" ht="43.2" spans="1:6">
+    <row r="150" ht="51" spans="1:6">
       <c r="A150" s="37"/>
       <c r="B150" s="37"/>
       <c r="C150" s="44" t="s">
@@ -9684,7 +9713,7 @@
       <c r="E150" s="40"/>
       <c r="F150" s="43"/>
     </row>
-    <row r="151" ht="129.6" spans="1:6">
+    <row r="151" ht="168" spans="1:6">
       <c r="A151" s="41"/>
       <c r="B151" s="41"/>
       <c r="C151" s="44" t="s">
@@ -9706,7 +9735,7 @@
       <c r="E152" s="17"/>
       <c r="F152" s="18"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" ht="17" spans="1:6">
       <c r="A153" s="4" t="s">
         <v>1</v>
       </c>
@@ -9742,7 +9771,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" ht="17" spans="1:6">
       <c r="A155" s="19"/>
       <c r="B155" s="20" t="s">
         <v>66</v>
@@ -9760,7 +9789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" ht="15.6" spans="1:6">
+    <row r="156" ht="18" spans="1:6">
       <c r="A156" s="34">
         <v>1</v>
       </c>
@@ -9776,7 +9805,7 @@
       <c r="E156" s="45"/>
       <c r="F156" s="43"/>
     </row>
-    <row r="157" ht="31.2" spans="1:6">
+    <row r="157" ht="53" spans="1:6">
       <c r="A157" s="37"/>
       <c r="B157" s="37"/>
       <c r="C157" s="35" t="s">
@@ -9788,7 +9817,7 @@
       <c r="E157" s="45"/>
       <c r="F157" s="43"/>
     </row>
-    <row r="158" ht="15.6" spans="1:6">
+    <row r="158" ht="17.6" spans="1:6">
       <c r="A158" s="37"/>
       <c r="B158" s="37"/>
       <c r="C158" s="11" t="s">
@@ -9800,7 +9829,7 @@
       <c r="E158" s="45"/>
       <c r="F158" s="43"/>
     </row>
-    <row r="159" ht="43.2" spans="1:6">
+    <row r="159" ht="51" spans="1:6">
       <c r="A159" s="37"/>
       <c r="B159" s="37"/>
       <c r="C159" s="46" t="s">
@@ -9826,7 +9855,7 @@
       </c>
       <c r="F160" s="43"/>
     </row>
-    <row r="161" ht="312" spans="1:6">
+    <row r="161" ht="370" spans="1:6">
       <c r="A161" s="37"/>
       <c r="B161" s="37"/>
       <c r="C161" s="26" t="s">
@@ -9840,7 +9869,7 @@
       </c>
       <c r="F161" s="43"/>
     </row>
-    <row r="162" ht="374.4" spans="1:6">
+    <row r="162" ht="409.5" spans="1:6">
       <c r="A162" s="37"/>
       <c r="B162" s="37"/>
       <c r="C162" s="35" t="s">
@@ -9854,7 +9883,7 @@
       </c>
       <c r="F162" s="43"/>
     </row>
-    <row r="163" ht="156" spans="1:6">
+    <row r="163" ht="212" spans="1:6">
       <c r="A163" s="37"/>
       <c r="B163" s="37"/>
       <c r="C163" s="35" t="s">
@@ -9866,7 +9895,7 @@
       <c r="E163" s="45"/>
       <c r="F163" s="43"/>
     </row>
-    <row r="164" ht="327.6" spans="1:6">
+    <row r="164" ht="388" spans="1:6">
       <c r="A164" s="37"/>
       <c r="B164" s="37"/>
       <c r="C164" s="35" t="s">
@@ -9878,7 +9907,7 @@
       <c r="E164" s="45"/>
       <c r="F164" s="43"/>
     </row>
-    <row r="165" ht="156" spans="1:6">
+    <row r="165" ht="194" spans="1:6">
       <c r="A165" s="37"/>
       <c r="B165" s="37"/>
       <c r="C165" s="35" t="s">
@@ -9890,7 +9919,7 @@
       <c r="E165" s="45"/>
       <c r="F165" s="43"/>
     </row>
-    <row r="166" ht="15.6" spans="1:6">
+    <row r="166" ht="18" spans="1:6">
       <c r="A166" s="37"/>
       <c r="B166" s="37"/>
       <c r="C166" s="35" t="s">
@@ -9902,7 +9931,7 @@
       <c r="E166" s="45"/>
       <c r="F166" s="43"/>
     </row>
-    <row r="167" ht="15.6" spans="1:6">
+    <row r="167" ht="18" spans="1:6">
       <c r="A167" s="37"/>
       <c r="B167" s="37"/>
       <c r="C167" s="35" t="s">
@@ -9914,7 +9943,7 @@
       <c r="E167" s="45"/>
       <c r="F167" s="43"/>
     </row>
-    <row r="168" ht="15.6" spans="1:6">
+    <row r="168" ht="18" spans="1:6">
       <c r="A168" s="37"/>
       <c r="B168" s="37"/>
       <c r="C168" s="35" t="s">
@@ -9926,7 +9955,7 @@
       <c r="E168" s="45"/>
       <c r="F168" s="43"/>
     </row>
-    <row r="169" ht="15.6" spans="1:6">
+    <row r="169" ht="18" spans="1:6">
       <c r="A169" s="37"/>
       <c r="B169" s="37"/>
       <c r="C169" s="35" t="s">
@@ -9938,7 +9967,7 @@
       <c r="E169" s="45"/>
       <c r="F169" s="43"/>
     </row>
-    <row r="170" ht="31.2" spans="1:6">
+    <row r="170" ht="36" spans="1:6">
       <c r="A170" s="37"/>
       <c r="B170" s="37"/>
       <c r="C170" s="35" t="s">
@@ -9950,7 +9979,7 @@
       <c r="E170" s="45"/>
       <c r="F170" s="43"/>
     </row>
-    <row r="171" ht="31.2" spans="1:6">
+    <row r="171" ht="36" spans="1:6">
       <c r="A171" s="37"/>
       <c r="B171" s="37"/>
       <c r="C171" s="35" t="s">
@@ -9962,7 +9991,7 @@
       <c r="E171" s="45"/>
       <c r="F171" s="43"/>
     </row>
-    <row r="172" ht="15.6" spans="1:6">
+    <row r="172" ht="18" spans="1:6">
       <c r="A172" s="37"/>
       <c r="B172" s="37"/>
       <c r="C172" s="35" t="s">
@@ -9974,7 +10003,7 @@
       <c r="E172" s="45"/>
       <c r="F172" s="43"/>
     </row>
-    <row r="173" ht="15.6" spans="1:6">
+    <row r="173" ht="18" spans="1:6">
       <c r="A173" s="37"/>
       <c r="B173" s="37"/>
       <c r="C173" s="35" t="s">
@@ -9984,7 +10013,7 @@
       <c r="E173" s="45"/>
       <c r="F173" s="43"/>
     </row>
-    <row r="174" ht="140.4" spans="1:6">
+    <row r="174" ht="159" spans="1:6">
       <c r="A174" s="37"/>
       <c r="B174" s="37"/>
       <c r="C174" s="35" t="s">
@@ -9996,7 +10025,7 @@
       <c r="E174" s="45"/>
       <c r="F174" s="43"/>
     </row>
-    <row r="175" ht="312" spans="1:6">
+    <row r="175" ht="370" spans="1:6">
       <c r="A175" s="41"/>
       <c r="B175" s="41"/>
       <c r="C175" s="35" t="s">
@@ -10018,7 +10047,7 @@
       <c r="E176" s="17"/>
       <c r="F176" s="18"/>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" ht="17" spans="1:6">
       <c r="A177" s="4" t="s">
         <v>1</v>
       </c>
@@ -10038,7 +10067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" ht="28.8" spans="1:6">
+    <row r="178" ht="34" spans="1:6">
       <c r="A178" s="5">
         <v>1</v>
       </c>
@@ -10054,7 +10083,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" ht="17" spans="1:6">
       <c r="A179" s="19"/>
       <c r="B179" s="20" t="s">
         <v>66</v>
@@ -10072,7 +10101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" ht="124.8" spans="1:6">
+    <row r="180" ht="141" spans="1:6">
       <c r="A180" s="47">
         <v>1</v>
       </c>
@@ -10088,7 +10117,7 @@
       <c r="E180" s="40"/>
       <c r="F180" s="43"/>
     </row>
-    <row r="181" ht="62.4" spans="1:6">
+    <row r="181" ht="88" spans="1:6">
       <c r="A181" s="47"/>
       <c r="B181" s="47"/>
       <c r="C181" s="35" t="s">
@@ -10100,7 +10129,7 @@
       <c r="E181" s="40"/>
       <c r="F181" s="43"/>
     </row>
-    <row r="182" ht="109.2" spans="1:6">
+    <row r="182" ht="124" spans="1:6">
       <c r="A182" s="47"/>
       <c r="B182" s="47"/>
       <c r="C182" s="35" t="s">
@@ -10112,7 +10141,7 @@
       <c r="E182" s="40"/>
       <c r="F182" s="43"/>
     </row>
-    <row r="183" ht="31.2" spans="1:6">
+    <row r="183" ht="36" spans="1:6">
       <c r="A183" s="47"/>
       <c r="B183" s="47"/>
       <c r="C183" s="35" t="s">
@@ -10124,7 +10153,7 @@
       <c r="E183" s="40"/>
       <c r="F183" s="43"/>
     </row>
-    <row r="184" ht="31.2" spans="1:6">
+    <row r="184" ht="36" spans="1:6">
       <c r="A184" s="47"/>
       <c r="B184" s="47"/>
       <c r="C184" s="35" t="s">
@@ -10136,7 +10165,7 @@
       <c r="E184" s="40"/>
       <c r="F184" s="43"/>
     </row>
-    <row r="185" ht="15.6" spans="1:6">
+    <row r="185" ht="18" spans="1:6">
       <c r="A185" s="47"/>
       <c r="B185" s="47"/>
       <c r="C185" s="35" t="s">
@@ -10148,7 +10177,7 @@
       <c r="E185" s="40"/>
       <c r="F185" s="43"/>
     </row>
-    <row r="186" ht="109.2" spans="1:6">
+    <row r="186" ht="124" spans="1:6">
       <c r="A186" s="47"/>
       <c r="B186" s="47"/>
       <c r="C186" s="35" t="s">
@@ -10170,7 +10199,7 @@
       <c r="E187" s="17"/>
       <c r="F187" s="18"/>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" ht="17" spans="1:6">
       <c r="A188" s="4" t="s">
         <v>1</v>
       </c>
@@ -10190,7 +10219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" ht="28.8" spans="1:6">
+    <row r="189" ht="34" spans="1:6">
       <c r="A189" s="5">
         <v>1</v>
       </c>
@@ -10206,7 +10235,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" ht="17" spans="1:6">
       <c r="A190" s="19"/>
       <c r="B190" s="20" t="s">
         <v>66</v>
@@ -10224,7 +10253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" ht="15.6" spans="1:6">
+    <row r="191" ht="17.6" spans="1:6">
       <c r="A191" s="47">
         <v>1</v>
       </c>
@@ -10240,7 +10269,7 @@
       <c r="E191" s="40"/>
       <c r="F191" s="43"/>
     </row>
-    <row r="192" ht="31.2" spans="1:6">
+    <row r="192" ht="36" spans="1:6">
       <c r="A192" s="47"/>
       <c r="B192" s="47"/>
       <c r="C192" s="35" t="s">
@@ -10252,7 +10281,7 @@
       <c r="E192" s="40"/>
       <c r="F192" s="43"/>
     </row>
-    <row r="193" ht="31.2" spans="1:6">
+    <row r="193" ht="36" spans="1:6">
       <c r="A193" s="47"/>
       <c r="B193" s="47"/>
       <c r="C193" s="35" t="s">
@@ -10264,7 +10293,7 @@
       <c r="E193" s="40"/>
       <c r="F193" s="43"/>
     </row>
-    <row r="194" ht="93.6" spans="1:6">
+    <row r="194" ht="106" spans="1:6">
       <c r="A194" s="47"/>
       <c r="B194" s="47"/>
       <c r="C194" s="35" t="s">
@@ -10276,7 +10305,7 @@
       <c r="E194" s="40"/>
       <c r="F194" s="43"/>
     </row>
-    <row r="195" ht="93.6" spans="1:6">
+    <row r="195" ht="124" spans="1:6">
       <c r="A195" s="47"/>
       <c r="B195" s="47"/>
       <c r="C195" s="35" t="s">
@@ -10288,7 +10317,7 @@
       <c r="E195" s="40"/>
       <c r="F195" s="43"/>
     </row>
-    <row r="196" ht="140.4" spans="1:6">
+    <row r="196" ht="159" spans="1:6">
       <c r="A196" s="47"/>
       <c r="B196" s="47"/>
       <c r="C196" s="35" t="s">
@@ -10300,7 +10329,7 @@
       <c r="E196" s="40"/>
       <c r="F196" s="43"/>
     </row>
-    <row r="197" ht="15.6" spans="1:6">
+    <row r="197" ht="17.6" spans="1:6">
       <c r="A197" s="47"/>
       <c r="B197" s="47"/>
       <c r="C197" s="48" t="s">
@@ -10312,7 +10341,7 @@
       <c r="E197" s="40"/>
       <c r="F197" s="43"/>
     </row>
-    <row r="198" ht="28.8" spans="1:6">
+    <row r="198" ht="34" spans="1:6">
       <c r="A198" s="47"/>
       <c r="B198" s="47"/>
       <c r="C198" s="49" t="s">
